--- a/orders.xlsx
+++ b/orders.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3904" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5349" uniqueCount="1350">
   <si>
     <t>Ngày tạo đơn</t>
   </si>
@@ -2981,6 +2981,1086 @@
   </si>
   <si>
     <t>Moi Lan</t>
+  </si>
+  <si>
+    <t>Anita Mohamad</t>
+  </si>
+  <si>
+    <t>17037629030770</t>
+  </si>
+  <si>
+    <t>Liew KF Yvonne</t>
+  </si>
+  <si>
+    <t>17037586858354</t>
+  </si>
+  <si>
+    <t>Freda E Lijawa</t>
+  </si>
+  <si>
+    <t>17037518799218</t>
+  </si>
+  <si>
+    <t>Joanne Khoo</t>
+  </si>
+  <si>
+    <t>17037414465906</t>
+  </si>
+  <si>
+    <t>05/08/2026</t>
+  </si>
+  <si>
+    <t>Ivy Yap</t>
+  </si>
+  <si>
+    <t>17036891488626</t>
+  </si>
+  <si>
+    <t>Evine Lee</t>
+  </si>
+  <si>
+    <t>Nancy Lim</t>
+  </si>
+  <si>
+    <t>Farrah Din</t>
+  </si>
+  <si>
+    <t>17036791120242</t>
+  </si>
+  <si>
+    <t>Anira Frank Peter</t>
+  </si>
+  <si>
+    <t>17036734660978</t>
+  </si>
+  <si>
+    <t>Helen Yeo</t>
+  </si>
+  <si>
+    <t>17036716048754</t>
+  </si>
+  <si>
+    <t>Lydia Kamal</t>
+  </si>
+  <si>
+    <t>17036692128114</t>
+  </si>
+  <si>
+    <t>17036676301170</t>
+  </si>
+  <si>
+    <t>Joyce David</t>
+  </si>
+  <si>
+    <t>17036627738994</t>
+  </si>
+  <si>
+    <t>Tan Ah Chu</t>
+  </si>
+  <si>
+    <t>Cho  yea moi</t>
+  </si>
+  <si>
+    <t>Angela Liew</t>
+  </si>
+  <si>
+    <t>Ema Shuaid</t>
+  </si>
+  <si>
+    <t>66532093362546</t>
+  </si>
+  <si>
+    <t>Sathia Prema</t>
+  </si>
+  <si>
+    <t>66531874701682</t>
+  </si>
+  <si>
+    <t>Michelle khor</t>
+  </si>
+  <si>
+    <t>17036471533938</t>
+  </si>
+  <si>
+    <t>May Lee</t>
+  </si>
+  <si>
+    <t>IVY PHOTOGRAPHY</t>
+  </si>
+  <si>
+    <t>17036419531122</t>
+  </si>
+  <si>
+    <t>Shereen Nadira</t>
+  </si>
+  <si>
+    <t>17036412518770</t>
+  </si>
+  <si>
+    <t>Lily chang</t>
+  </si>
+  <si>
+    <t>17036406522226</t>
+  </si>
+  <si>
+    <t>Karen Lai Wui Ling</t>
+  </si>
+  <si>
+    <t>17036370248050</t>
+  </si>
+  <si>
+    <t>Mazuin Sulaiman</t>
+  </si>
+  <si>
+    <t>17036348162418</t>
+  </si>
+  <si>
+    <t>Herawati Arang</t>
+  </si>
+  <si>
+    <t>66531026698610</t>
+  </si>
+  <si>
+    <t>Zakiah binti Zahib</t>
+  </si>
+  <si>
+    <t>17036277711218</t>
+  </si>
+  <si>
+    <t>Nur Alia</t>
+  </si>
+  <si>
+    <t>66530922660210</t>
+  </si>
+  <si>
+    <t>Doreen Chew</t>
+  </si>
+  <si>
+    <t>17036261851506</t>
+  </si>
+  <si>
+    <t>CO_1</t>
+  </si>
+  <si>
+    <t>Zahiah bt. Meor Alif</t>
+  </si>
+  <si>
+    <t>17036237078898</t>
+  </si>
+  <si>
+    <t>120253483200390712</t>
+  </si>
+  <si>
+    <t>kho joey</t>
+  </si>
+  <si>
+    <t>66530813247858</t>
+  </si>
+  <si>
+    <t>Azora Abdullah</t>
+  </si>
+  <si>
+    <t>17036142674290</t>
+  </si>
+  <si>
+    <t>120249407152060262</t>
+  </si>
+  <si>
+    <t>NASYLIA BT MAGI</t>
+  </si>
+  <si>
+    <t>17036086149490</t>
+  </si>
+  <si>
+    <t>17036076220786</t>
+  </si>
+  <si>
+    <t>Raja Shahrul Bariyah Binti Raja Ismail Shahrul Bariyah Binti Raja Ismail</t>
+  </si>
+  <si>
+    <t>17036065931634</t>
+  </si>
+  <si>
+    <t>NOORAZIZAH SHAIKH ESMAIL</t>
+  </si>
+  <si>
+    <t>17036052758898</t>
+  </si>
+  <si>
+    <t>Resia Nyalo</t>
+  </si>
+  <si>
+    <t>17036052365682</t>
+  </si>
+  <si>
+    <t>Browse_2</t>
+  </si>
+  <si>
+    <t>17035997741426</t>
+  </si>
+  <si>
+    <t>sag_organic</t>
+  </si>
+  <si>
+    <t>eddy wana</t>
+  </si>
+  <si>
+    <t>17035987190130</t>
+  </si>
+  <si>
+    <t>Ijan Haini</t>
+  </si>
+  <si>
+    <t>17035929649522</t>
+  </si>
+  <si>
+    <t>Ain Sabli</t>
+  </si>
+  <si>
+    <t>17035925782898</t>
+  </si>
+  <si>
+    <t>Connie ng</t>
+  </si>
+  <si>
+    <t>17035919458674</t>
+  </si>
+  <si>
+    <t>LINDA RAHIM ABDUL RAHIM</t>
+  </si>
+  <si>
+    <t>17035909366130</t>
+  </si>
+  <si>
+    <t>Tan Lizzie</t>
+  </si>
+  <si>
+    <t>Ummi Rozana Khasim Rozana binti khasim</t>
+  </si>
+  <si>
+    <t>66529366016370</t>
+  </si>
+  <si>
+    <t>Masitah Mohd</t>
+  </si>
+  <si>
+    <t>17035863294322</t>
+  </si>
+  <si>
+    <t>Rubie Latif</t>
+  </si>
+  <si>
+    <t>17035811062130</t>
+  </si>
+  <si>
+    <t>Azlina Awang</t>
+  </si>
+  <si>
+    <t>17035810046322</t>
+  </si>
+  <si>
+    <t>120248868679950262</t>
+  </si>
+  <si>
+    <t>Rahimah Mohamad</t>
+  </si>
+  <si>
+    <t>17035687919986</t>
+  </si>
+  <si>
+    <t>120248868421350262</t>
+  </si>
+  <si>
+    <t>Hasnita Hassan</t>
+  </si>
+  <si>
+    <t>17035687100786</t>
+  </si>
+  <si>
+    <t>120249229950140262</t>
+  </si>
+  <si>
+    <t>Oliver Lydia Yibit</t>
+  </si>
+  <si>
+    <t>17035665178994</t>
+  </si>
+  <si>
+    <t>Sajea Arefin Prema Prema</t>
+  </si>
+  <si>
+    <t>66527897977202</t>
+  </si>
+  <si>
+    <t>Jd Ooi</t>
+  </si>
+  <si>
+    <t>17035098456434</t>
+  </si>
+  <si>
+    <t>04/08/2026</t>
+  </si>
+  <si>
+    <t>THEEPAH MAHEN</t>
+  </si>
+  <si>
+    <t>17034936222066</t>
+  </si>
+  <si>
+    <t>Nurul Ain Rusman</t>
+  </si>
+  <si>
+    <t>17034858201458</t>
+  </si>
+  <si>
+    <t>Pearly Leong Pearly Leong</t>
+  </si>
+  <si>
+    <t>17034660282738</t>
+  </si>
+  <si>
+    <t>Tan LoyKiew</t>
+  </si>
+  <si>
+    <t>Siti Aminah</t>
+  </si>
+  <si>
+    <t>17034575937906</t>
+  </si>
+  <si>
+    <t>ROZIHA RASHID</t>
+  </si>
+  <si>
+    <t>17033990570354</t>
+  </si>
+  <si>
+    <t>Bee Bens</t>
+  </si>
+  <si>
+    <t>17033986605426</t>
+  </si>
+  <si>
+    <t>yuhanis jaffar</t>
+  </si>
+  <si>
+    <t>17033983361394</t>
+  </si>
+  <si>
+    <t>Jong Jong</t>
+  </si>
+  <si>
+    <t>66525543137650</t>
+  </si>
+  <si>
+    <t>Sue Zana</t>
+  </si>
+  <si>
+    <t>17033910944114</t>
+  </si>
+  <si>
+    <t>WEI YEE CHOW</t>
+  </si>
+  <si>
+    <t>17033888596338</t>
+  </si>
+  <si>
+    <t>Mahligai koh enterprise Cxia</t>
+  </si>
+  <si>
+    <t>17033851928946</t>
+  </si>
+  <si>
+    <t>120249229472690262</t>
+  </si>
+  <si>
+    <t>Julia S.</t>
+  </si>
+  <si>
+    <t>17033808150898</t>
+  </si>
+  <si>
+    <t>Elaine How</t>
+  </si>
+  <si>
+    <t>17033797468530</t>
+  </si>
+  <si>
+    <t>Anis Mohammed</t>
+  </si>
+  <si>
+    <t>17033756377458</t>
+  </si>
+  <si>
+    <t>Nur Hasni Che Had</t>
+  </si>
+  <si>
+    <t>17033753297266</t>
+  </si>
+  <si>
+    <t>Siti Juliana Bakar</t>
+  </si>
+  <si>
+    <t>66525070295410</t>
+  </si>
+  <si>
+    <t>Nana Haris</t>
+  </si>
+  <si>
+    <t>17033674097010</t>
+  </si>
+  <si>
+    <t>toh yew ling</t>
+  </si>
+  <si>
+    <t>Andrew soong</t>
+  </si>
+  <si>
+    <t>17033630744946</t>
+  </si>
+  <si>
+    <t>Cindy Lau</t>
+  </si>
+  <si>
+    <t>Norfadhlina Khalid</t>
+  </si>
+  <si>
+    <t>17033554329970</t>
+  </si>
+  <si>
+    <t>Siti Maryam Md Nor</t>
+  </si>
+  <si>
+    <t>17033532801394</t>
+  </si>
+  <si>
+    <t>Marlina Reni</t>
+  </si>
+  <si>
+    <t>17033513894258</t>
+  </si>
+  <si>
+    <t>JUWAINI ABU BAKAR</t>
+  </si>
+  <si>
+    <t>17033510715762</t>
+  </si>
+  <si>
+    <t>Noraisah idris</t>
+  </si>
+  <si>
+    <t>17033503146354</t>
+  </si>
+  <si>
+    <t>MPG_Jul31_Engagement_ThisOrThat</t>
+  </si>
+  <si>
+    <t>Ling Leh Hung Ling</t>
+  </si>
+  <si>
+    <t>17033490268530</t>
+  </si>
+  <si>
+    <t>SauChun Leong</t>
+  </si>
+  <si>
+    <t>120252922477470712</t>
+  </si>
+  <si>
+    <t>Wey jin Cheong</t>
+  </si>
+  <si>
+    <t>17033341174130</t>
+  </si>
+  <si>
+    <t>Cathy liew</t>
+  </si>
+  <si>
+    <t>Shirley Lu</t>
+  </si>
+  <si>
+    <t>17033269805426</t>
+  </si>
+  <si>
+    <t>120252922477430712</t>
+  </si>
+  <si>
+    <t>Huei hiang Lim</t>
+  </si>
+  <si>
+    <t>MPG_Jul29_Education_Anti-AgingTips</t>
+  </si>
+  <si>
+    <t>JALIUS BIN RAYMOND</t>
+  </si>
+  <si>
+    <t>17033056518514</t>
+  </si>
+  <si>
+    <t>Noraini Razali</t>
+  </si>
+  <si>
+    <t>17032851095922</t>
+  </si>
+  <si>
+    <t>Noraini Razali Razali</t>
+  </si>
+  <si>
+    <t>17032835793266</t>
+  </si>
+  <si>
+    <t>Nisa Ung</t>
+  </si>
+  <si>
+    <t>17032753971570</t>
+  </si>
+  <si>
+    <t>03/08/2026</t>
+  </si>
+  <si>
+    <t>Dayang zalikha</t>
+  </si>
+  <si>
+    <t>17032400372082</t>
+  </si>
+  <si>
+    <t>Monalisa</t>
+  </si>
+  <si>
+    <t>KARIMAH AB.GHANI</t>
+  </si>
+  <si>
+    <t>66521431376242</t>
+  </si>
+  <si>
+    <t>Calvin Ah King Ah King</t>
+  </si>
+  <si>
+    <t>17032334541170</t>
+  </si>
+  <si>
+    <t>NORZILAH BINTI AMIR Amir</t>
+  </si>
+  <si>
+    <t>17032284045682</t>
+  </si>
+  <si>
+    <t>DENAI QASEH</t>
+  </si>
+  <si>
+    <t>17032224145778</t>
+  </si>
+  <si>
+    <t>Goo</t>
+  </si>
+  <si>
+    <t>ZABARIAH BINTI OMAR OMAR</t>
+  </si>
+  <si>
+    <t>17032214872434</t>
+  </si>
+  <si>
+    <t>Lee Shiau vui</t>
+  </si>
+  <si>
+    <t>17032211628402</t>
+  </si>
+  <si>
+    <t>NOOR SHAFIHAH Shamsudin</t>
+  </si>
+  <si>
+    <t>66521111363954</t>
+  </si>
+  <si>
+    <t>Nurha Muhammad</t>
+  </si>
+  <si>
+    <t>17032145043826</t>
+  </si>
+  <si>
+    <t>CATHERINE PAUL ROSLI</t>
+  </si>
+  <si>
+    <t>17032142225778</t>
+  </si>
+  <si>
+    <t>rahmah mat yussof</t>
+  </si>
+  <si>
+    <t>17032118272370</t>
+  </si>
+  <si>
+    <t>120249110169390262</t>
+  </si>
+  <si>
+    <t>Nur Hayati Anuar</t>
+  </si>
+  <si>
+    <t>Teresa china Anyie</t>
+  </si>
+  <si>
+    <t>17032078754162</t>
+  </si>
+  <si>
+    <t>120249229950220262</t>
+  </si>
+  <si>
+    <t>Saiful Shamsuddin</t>
+  </si>
+  <si>
+    <t>17032068923762</t>
+  </si>
+  <si>
+    <t>seri Wirdaningsih</t>
+  </si>
+  <si>
+    <t>17032058634610</t>
+  </si>
+  <si>
+    <t>Scholastica Kusong</t>
+  </si>
+  <si>
+    <t>66520763466098</t>
+  </si>
+  <si>
+    <t>120246875704990262</t>
+  </si>
+  <si>
+    <t>wan Zulita</t>
+  </si>
+  <si>
+    <t>17031985561970</t>
+  </si>
+  <si>
+    <t>Qamariah Adi</t>
+  </si>
+  <si>
+    <t>17031851770226</t>
+  </si>
+  <si>
+    <t>NL Wong</t>
+  </si>
+  <si>
+    <t>17031826801010</t>
+  </si>
+  <si>
+    <t>WaiLeng Tham</t>
+  </si>
+  <si>
+    <t>17031796228466</t>
+  </si>
+  <si>
+    <t>Araa Arash</t>
+  </si>
+  <si>
+    <t>17031762542962</t>
+  </si>
+  <si>
+    <t>17031728169330</t>
+  </si>
+  <si>
+    <t>Nur aisyah alisa</t>
+  </si>
+  <si>
+    <t>17031715160434</t>
+  </si>
+  <si>
+    <t>Aisha Yaacob</t>
+  </si>
+  <si>
+    <t>17031672234354</t>
+  </si>
+  <si>
+    <t>Norimah Mohd Salleh</t>
+  </si>
+  <si>
+    <t>17031544799602</t>
+  </si>
+  <si>
+    <t>Adel Kamil</t>
+  </si>
+  <si>
+    <t>17031479492978</t>
+  </si>
+  <si>
+    <t>Mdm NurVie Hmz</t>
+  </si>
+  <si>
+    <t>17031022346610</t>
+  </si>
+  <si>
+    <t>02/08/2026</t>
+  </si>
+  <si>
+    <t>jennie kang</t>
+  </si>
+  <si>
+    <t>17030875152754</t>
+  </si>
+  <si>
+    <t>120249476886560262</t>
+  </si>
+  <si>
+    <t>Clarice Dora</t>
+  </si>
+  <si>
+    <t>17030810501490</t>
+  </si>
+  <si>
+    <t>120249476075750262</t>
+  </si>
+  <si>
+    <t>Ng may loo</t>
+  </si>
+  <si>
+    <t>120251622683180577</t>
+  </si>
+  <si>
+    <t>Pat Loo</t>
+  </si>
+  <si>
+    <t>17030801523058</t>
+  </si>
+  <si>
+    <t>Atie Yusoff</t>
+  </si>
+  <si>
+    <t>17030799589746</t>
+  </si>
+  <si>
+    <t>Tina Shik</t>
+  </si>
+  <si>
+    <t>17030788940146</t>
+  </si>
+  <si>
+    <t>Effie Shariff</t>
+  </si>
+  <si>
+    <t>66516485898610</t>
+  </si>
+  <si>
+    <t>Padma Marathamuthan</t>
+  </si>
+  <si>
+    <t>17030495306098</t>
+  </si>
+  <si>
+    <t>Jesephine Then</t>
+  </si>
+  <si>
+    <t>17030494683506</t>
+  </si>
+  <si>
+    <t>Asnimah A</t>
+  </si>
+  <si>
+    <t>17030438388082</t>
+  </si>
+  <si>
+    <t>Norhanani Abd Rahman</t>
+  </si>
+  <si>
+    <t>17030339395954</t>
+  </si>
+  <si>
+    <t>Irene</t>
+  </si>
+  <si>
+    <t>Chock Shen Wai</t>
+  </si>
+  <si>
+    <t>17030309740914</t>
+  </si>
+  <si>
+    <t>NOORMALIA HARUN</t>
+  </si>
+  <si>
+    <t>17030295748978</t>
+  </si>
+  <si>
+    <t>eila aleela</t>
+  </si>
+  <si>
+    <t>17030231982450</t>
+  </si>
+  <si>
+    <t>Ramis Ayasamy</t>
+  </si>
+  <si>
+    <t>17030194266482</t>
+  </si>
+  <si>
+    <t>17030179389810</t>
+  </si>
+  <si>
+    <t>Jackie Teh</t>
+  </si>
+  <si>
+    <t>17030127878514</t>
+  </si>
+  <si>
+    <t>Suziliana Solhi</t>
+  </si>
+  <si>
+    <t>17030121193842</t>
+  </si>
+  <si>
+    <t>1871932077019282</t>
+  </si>
+  <si>
+    <t>Tuan Khatijah Tuan Husin</t>
+  </si>
+  <si>
+    <t>17030078300530</t>
+  </si>
+  <si>
+    <t>MAILIN SANTANI</t>
+  </si>
+  <si>
+    <t>Norashikin Bt Mamat Shikin</t>
+  </si>
+  <si>
+    <t>17029994611058</t>
+  </si>
+  <si>
+    <t>Salwa Azlan</t>
+  </si>
+  <si>
+    <t>17029970821490</t>
+  </si>
+  <si>
+    <t>Miria Hasbie</t>
+  </si>
+  <si>
+    <t>17029951324530</t>
+  </si>
+  <si>
+    <t>Anna Tan</t>
+  </si>
+  <si>
+    <t>17029941887346</t>
+  </si>
+  <si>
+    <t>Angela Yee</t>
+  </si>
+  <si>
+    <t>17029930746226</t>
+  </si>
+  <si>
+    <t>Azlina Mohd Afandi</t>
+  </si>
+  <si>
+    <t>17029902729586</t>
+  </si>
+  <si>
+    <t>17029893423474</t>
+  </si>
+  <si>
+    <t>Faridah Hanit</t>
+  </si>
+  <si>
+    <t>17029874418034</t>
+  </si>
+  <si>
+    <t>120249407152020262</t>
+  </si>
+  <si>
+    <t>Masdiana binti Abdul Rasid Diana</t>
+  </si>
+  <si>
+    <t>17029843026290</t>
+  </si>
+  <si>
+    <t>Nurafida</t>
+  </si>
+  <si>
+    <t>17029788238194</t>
+  </si>
+  <si>
+    <t>Novie Rahaeni</t>
+  </si>
+  <si>
+    <t>17029689704818</t>
+  </si>
+  <si>
+    <t>Low Sherlin</t>
+  </si>
+  <si>
+    <t>17029689540978</t>
+  </si>
+  <si>
+    <t>Malisa Musa</t>
+  </si>
+  <si>
+    <t>17029274894706</t>
+  </si>
+  <si>
+    <t>Benson Kee</t>
+  </si>
+  <si>
+    <t>Umira binti ali binti ali</t>
+  </si>
+  <si>
+    <t>17028601577842</t>
+  </si>
+  <si>
+    <t>01/08/2026</t>
+  </si>
+  <si>
+    <t>Nordiana Mohamad</t>
+  </si>
+  <si>
+    <t>17027811574130</t>
+  </si>
+  <si>
+    <t>120249476886510262</t>
+  </si>
+  <si>
+    <t>Nur Zafirah Binti Mohd Ariffin</t>
+  </si>
+  <si>
+    <t>17027754918258</t>
+  </si>
+  <si>
+    <t>shima yusoff</t>
+  </si>
+  <si>
+    <t>17027568894322</t>
+  </si>
+  <si>
+    <t>Abbie Chia</t>
+  </si>
+  <si>
+    <t>17027556671858</t>
+  </si>
+  <si>
+    <t>Faezah Mukri</t>
+  </si>
+  <si>
+    <t>Choy Yau</t>
+  </si>
+  <si>
+    <t>17027448832370</t>
+  </si>
+  <si>
+    <t>Hajar Maryam Mohamed Hashim</t>
+  </si>
+  <si>
+    <t>17027341615474</t>
+  </si>
+  <si>
+    <t>Lilik setyowati</t>
+  </si>
+  <si>
+    <t>66510469955954</t>
+  </si>
+  <si>
+    <t>Emma Bakar</t>
+  </si>
+  <si>
+    <t>17027237413234</t>
+  </si>
+  <si>
+    <t>A Wahab A Raman</t>
+  </si>
+  <si>
+    <t>66510196965746</t>
+  </si>
+  <si>
+    <t>Hidayati Abidin</t>
+  </si>
+  <si>
+    <t>Faam Lee Lee / Ngiam Kia Tong</t>
+  </si>
+  <si>
+    <t>17027020652914</t>
+  </si>
+  <si>
+    <t>Saffyah Saari</t>
+  </si>
+  <si>
+    <t>17026987065714</t>
+  </si>
+  <si>
+    <t>Siti Fauziah binti Syed Ariffin</t>
+  </si>
+  <si>
+    <t>17026959835506</t>
+  </si>
+  <si>
+    <t>shima nasir</t>
+  </si>
+  <si>
+    <t>17026936602994</t>
+  </si>
+  <si>
+    <t>Shoba G Gopalan</t>
+  </si>
+  <si>
+    <t>17026875228530</t>
+  </si>
+  <si>
+    <t>Jessicca Gereman</t>
+  </si>
+  <si>
+    <t>66508914819442</t>
+  </si>
+  <si>
+    <t>Aidatul Izana</t>
+  </si>
+  <si>
+    <t>17026750579058</t>
+  </si>
+  <si>
+    <t>120249407152010262</t>
+  </si>
+  <si>
+    <t>Nurul Iswani Ismail</t>
+  </si>
+  <si>
+    <t>17026712732018</t>
+  </si>
+  <si>
+    <t>Nia yap</t>
+  </si>
+  <si>
+    <t>17026698609010</t>
+  </si>
+  <si>
+    <t>Chan Joo Ee</t>
+  </si>
+  <si>
+    <t>Aisyah Jubri</t>
+  </si>
+  <si>
+    <t>17026687730034</t>
+  </si>
+  <si>
+    <t>Abdah Adzimah Che Md Noor</t>
+  </si>
+  <si>
+    <t>17026674884978</t>
+  </si>
+  <si>
+    <t>Aliza Mohamed</t>
+  </si>
+  <si>
+    <t>17026586345842</t>
+  </si>
+  <si>
+    <t>Danie Hamdanie Wan Mohamad</t>
+  </si>
+  <si>
+    <t>17026532180338</t>
+  </si>
+  <si>
+    <t>120249407152140262</t>
+  </si>
+  <si>
+    <t>Lavender Lim SY Lim</t>
+  </si>
+  <si>
+    <t>17024938967410</t>
   </si>
 </sst>
 </file>
@@ -3374,7 +4454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J501"/>
+  <dimension ref="A1:J685"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="10" width="25" customWidth="1"/>
@@ -19412,6 +20492,5894 @@
         <v>17</v>
       </c>
     </row>
+    <row r="502" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A502" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="B502" s="3">
+        <v>1</v>
+      </c>
+      <c r="C502" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D502" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E502" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="F502" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G502" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="H502" s="3">
+        <v>69</v>
+      </c>
+      <c r="I502" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J502" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="503" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A503" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="B503" s="3">
+        <v>1</v>
+      </c>
+      <c r="C503" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D503" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E503" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="F503" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G503" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="H503" s="3">
+        <v>69</v>
+      </c>
+      <c r="I503" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J503" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="504" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A504" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="B504" s="3">
+        <v>2</v>
+      </c>
+      <c r="C504" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D504" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E504" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="F504" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G504" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="H504" s="3">
+        <v>473</v>
+      </c>
+      <c r="I504" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J504" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="505" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A505" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="B505" s="3">
+        <v>3</v>
+      </c>
+      <c r="C505" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D505" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E505" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="F505" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G505" s="3">
+        <v>2187929</v>
+      </c>
+      <c r="H505" s="3">
+        <v>75</v>
+      </c>
+      <c r="I505" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="J505" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="506" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A506" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="B506" s="3">
+        <v>8</v>
+      </c>
+      <c r="C506" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D506" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E506" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="F506" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G506" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="H506" s="3">
+        <v>269</v>
+      </c>
+      <c r="I506" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J506" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="507" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A507" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B507" s="3">
+        <v>1</v>
+      </c>
+      <c r="C507" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D507" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E507" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="F507" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G507" s="3" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H507" s="3">
+        <v>193</v>
+      </c>
+      <c r="I507" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J507" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="508" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A508" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B508" s="3">
+        <v>3</v>
+      </c>
+      <c r="C508" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D508" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E508" s="3" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F508" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G508" s="3">
+        <v>2187840</v>
+      </c>
+      <c r="H508" s="3">
+        <v>179</v>
+      </c>
+      <c r="I508" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J508" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="509" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A509" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B509" s="3">
+        <v>3</v>
+      </c>
+      <c r="C509" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D509" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E509" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F509" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G509" s="3">
+        <v>2187834</v>
+      </c>
+      <c r="H509" s="3">
+        <v>125</v>
+      </c>
+      <c r="I509" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J509" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="510" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A510" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B510" s="3">
+        <v>2</v>
+      </c>
+      <c r="C510" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D510" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E510" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F510" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G510" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H510" s="3">
+        <v>175</v>
+      </c>
+      <c r="I510" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J510" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="511" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A511" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B511" s="3">
+        <v>2</v>
+      </c>
+      <c r="C511" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D511" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E511" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F511" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G511" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H511" s="3">
+        <v>67</v>
+      </c>
+      <c r="I511" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J511" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="512" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A512" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B512" s="3">
+        <v>6</v>
+      </c>
+      <c r="C512" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D512" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E512" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F512" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G512" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H512" s="3">
+        <v>64.75</v>
+      </c>
+      <c r="I512" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J512" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="513" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A513" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B513" s="3">
+        <v>3</v>
+      </c>
+      <c r="C513" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D513" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="E513" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F513" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G513" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H513" s="3">
+        <v>129</v>
+      </c>
+      <c r="I513" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J513" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="514" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A514" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B514" s="3">
+        <v>6</v>
+      </c>
+      <c r="C514" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D514" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E514" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F514" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G514" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H514" s="3">
+        <v>195</v>
+      </c>
+      <c r="I514" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J514" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="515" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A515" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B515" s="3">
+        <v>1</v>
+      </c>
+      <c r="C515" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D515" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E515" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F515" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G515" s="3" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H515" s="3">
+        <v>194</v>
+      </c>
+      <c r="I515" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J515" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="516" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A516" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B516" s="3">
+        <v>5</v>
+      </c>
+      <c r="C516" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D516" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E516" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F516" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G516" s="3">
+        <v>2187696</v>
+      </c>
+      <c r="H516" s="3">
+        <v>169</v>
+      </c>
+      <c r="I516" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J516" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="517" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A517" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B517" s="3">
+        <v>4</v>
+      </c>
+      <c r="C517" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D517" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="E517" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F517" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G517" s="3">
+        <v>2187686</v>
+      </c>
+      <c r="H517" s="3">
+        <v>129</v>
+      </c>
+      <c r="I517" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J517" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="518" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A518" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B518" s="3">
+        <v>6</v>
+      </c>
+      <c r="C518" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D518" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E518" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F518" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G518" s="3">
+        <v>2187681</v>
+      </c>
+      <c r="H518" s="3">
+        <v>72</v>
+      </c>
+      <c r="I518" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J518" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="519" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A519" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B519" s="3">
+        <v>1</v>
+      </c>
+      <c r="C519" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D519" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E519" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F519" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G519" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H519" s="3">
+        <v>138</v>
+      </c>
+      <c r="I519" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J519" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="520" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A520" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B520" s="3">
+        <v>5</v>
+      </c>
+      <c r="C520" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D520" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E520" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F520" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G520" s="3" t="s">
+        <v>1020</v>
+      </c>
+      <c r="H520" s="3">
+        <v>126</v>
+      </c>
+      <c r="I520" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J520" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="521" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A521" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B521" s="3">
+        <v>1</v>
+      </c>
+      <c r="C521" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D521" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E521" s="3" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F521" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G521" s="3">
+        <v>2187566</v>
+      </c>
+      <c r="H521" s="3">
+        <v>129</v>
+      </c>
+      <c r="I521" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J521" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="522" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A522" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B522" s="3">
+        <v>5</v>
+      </c>
+      <c r="C522" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D522" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E522" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F522" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G522" s="3" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H522" s="3">
+        <v>183</v>
+      </c>
+      <c r="I522" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J522" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="523" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A523" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B523" s="3">
+        <v>1</v>
+      </c>
+      <c r="C523" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D523" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E523" s="3" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F523" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G523" s="3">
+        <v>2187545</v>
+      </c>
+      <c r="H523" s="3">
+        <v>75</v>
+      </c>
+      <c r="I523" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J523" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="524" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A524" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B524" s="3">
+        <v>1</v>
+      </c>
+      <c r="C524" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D524" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E524" s="3" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F524" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G524" s="3" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H524" s="3">
+        <v>333</v>
+      </c>
+      <c r="I524" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J524" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="525" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A525" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B525" s="3">
+        <v>1</v>
+      </c>
+      <c r="C525" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D525" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E525" s="3" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F525" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G525" s="3" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H525" s="3">
+        <v>183</v>
+      </c>
+      <c r="I525" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J525" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="526" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A526" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B526" s="3">
+        <v>4</v>
+      </c>
+      <c r="C526" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D526" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E526" s="3" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F526" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G526" s="3" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H526" s="3">
+        <v>136</v>
+      </c>
+      <c r="I526" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J526" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="527" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A527" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B527" s="3">
+        <v>54</v>
+      </c>
+      <c r="C527" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D527" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E527" s="3" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F527" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G527" s="3" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H527" s="3">
+        <v>126</v>
+      </c>
+      <c r="I527" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J527" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="528" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A528" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B528" s="3">
+        <v>1</v>
+      </c>
+      <c r="C528" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D528" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E528" s="3" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F528" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G528" s="3" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H528" s="3">
+        <v>116</v>
+      </c>
+      <c r="I528" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J528" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="529" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A529" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B529" s="3">
+        <v>2</v>
+      </c>
+      <c r="C529" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D529" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E529" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F529" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G529" s="3" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H529" s="3">
+        <v>59</v>
+      </c>
+      <c r="I529" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J529" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="530" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A530" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B530" s="3">
+        <v>8</v>
+      </c>
+      <c r="C530" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D530" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E530" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F530" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G530" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H530" s="3">
+        <v>132</v>
+      </c>
+      <c r="I530" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J530" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="531" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A531" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B531" s="3">
+        <v>2</v>
+      </c>
+      <c r="C531" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D531" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E531" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F531" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G531" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="H531" s="3">
+        <v>119</v>
+      </c>
+      <c r="I531" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J531" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="532" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A532" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B532" s="3">
+        <v>1</v>
+      </c>
+      <c r="C532" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D532" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E532" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F532" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G532" s="3" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H532" s="3">
+        <v>132</v>
+      </c>
+      <c r="I532" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J532" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="533" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A533" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B533" s="3">
+        <v>1</v>
+      </c>
+      <c r="C533" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D533" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E533" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F533" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G533" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H533" s="3">
+        <v>67</v>
+      </c>
+      <c r="I533" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J533" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="534" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A534" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B534" s="3">
+        <v>6</v>
+      </c>
+      <c r="C534" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D534" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E534" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F534" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G534" s="3">
+        <v>2187236</v>
+      </c>
+      <c r="H534" s="3">
+        <v>129</v>
+      </c>
+      <c r="I534" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J534" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="535" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A535" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B535" s="3">
+        <v>4</v>
+      </c>
+      <c r="C535" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D535" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E535" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="F535" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G535" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H535" s="3">
+        <v>169</v>
+      </c>
+      <c r="I535" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J535" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="536" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A536" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B536" s="3">
+        <v>1</v>
+      </c>
+      <c r="C536" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D536" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E536" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F536" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G536" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H536" s="3">
+        <v>235</v>
+      </c>
+      <c r="I536" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J536" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="537" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A537" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B537" s="3">
+        <v>9</v>
+      </c>
+      <c r="C537" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D537" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E537" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F537" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G537" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H537" s="3">
+        <v>67</v>
+      </c>
+      <c r="I537" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J537" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="538" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A538" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B538" s="3">
+        <v>9</v>
+      </c>
+      <c r="C538" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D538" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E538" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F538" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G538" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="H538" s="3">
+        <v>183</v>
+      </c>
+      <c r="I538" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J538" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="539" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A539" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B539" s="3">
+        <v>2</v>
+      </c>
+      <c r="C539" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D539" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="E539" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F539" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G539" s="3" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H539" s="3">
+        <v>134</v>
+      </c>
+      <c r="I539" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J539" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="540" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A540" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B540" s="3">
+        <v>4</v>
+      </c>
+      <c r="C540" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D540" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E540" s="3" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F540" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G540" s="3" t="s">
+        <v>1057</v>
+      </c>
+      <c r="H540" s="3">
+        <v>194</v>
+      </c>
+      <c r="I540" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J540" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="541" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A541" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B541" s="3">
+        <v>3</v>
+      </c>
+      <c r="C541" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D541" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E541" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F541" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G541" s="3" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H541" s="3">
+        <v>183</v>
+      </c>
+      <c r="I541" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J541" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="542" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A542" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B542" s="3">
+        <v>2</v>
+      </c>
+      <c r="C542" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D542" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E542" s="3" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F542" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G542" s="3" t="s">
+        <v>1061</v>
+      </c>
+      <c r="H542" s="3">
+        <v>229</v>
+      </c>
+      <c r="I542" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J542" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="543" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A543" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B543" s="3">
+        <v>3</v>
+      </c>
+      <c r="C543" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D543" s="3" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E543" s="3" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F543" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G543" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="H543" s="3">
+        <v>136</v>
+      </c>
+      <c r="I543" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J543" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="544" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A544" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B544" s="3">
+        <v>3</v>
+      </c>
+      <c r="C544" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D544" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E544" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F544" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G544" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="H544" s="3">
+        <v>183</v>
+      </c>
+      <c r="I544" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J544" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="545" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A545" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B545" s="3">
+        <v>2</v>
+      </c>
+      <c r="C545" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D545" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E545" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F545" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G545" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="H545" s="3">
+        <v>69</v>
+      </c>
+      <c r="I545" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J545" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="546" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A546" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B546" s="3">
+        <v>10</v>
+      </c>
+      <c r="C546" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D546" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E546" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F546" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G546" s="3" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H546" s="3">
+        <v>204</v>
+      </c>
+      <c r="I546" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J546" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="547" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A547" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B547" s="3">
+        <v>15</v>
+      </c>
+      <c r="C547" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D547" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E547" s="3" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F547" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G547" s="3" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H547" s="3">
+        <v>183</v>
+      </c>
+      <c r="I547" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J547" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="548" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A548" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B548" s="3">
+        <v>3</v>
+      </c>
+      <c r="C548" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D548" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E548" s="3" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F548" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G548" s="3">
+        <v>2186922</v>
+      </c>
+      <c r="H548" s="3">
+        <v>72</v>
+      </c>
+      <c r="I548" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J548" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="549" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A549" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B549" s="3">
+        <v>6</v>
+      </c>
+      <c r="C549" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D549" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E549" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F549" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G549" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H549" s="3">
+        <v>199</v>
+      </c>
+      <c r="I549" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J549" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="550" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A550" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B550" s="3">
+        <v>5</v>
+      </c>
+      <c r="C550" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D550" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E550" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F550" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G550" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="H550" s="3">
+        <v>67</v>
+      </c>
+      <c r="I550" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J550" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="551" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A551" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B551" s="3">
+        <v>2</v>
+      </c>
+      <c r="C551" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D551" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E551" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F551" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G551" s="3" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H551" s="3">
+        <v>138</v>
+      </c>
+      <c r="I551" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J551" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="552" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A552" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B552" s="3">
+        <v>3</v>
+      </c>
+      <c r="C552" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D552" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E552" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F552" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G552" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="H552" s="3">
+        <v>136</v>
+      </c>
+      <c r="I552" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J552" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="553" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A553" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B553" s="3">
+        <v>1</v>
+      </c>
+      <c r="C553" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D553" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E553" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F553" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G553" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H553" s="3">
+        <v>119</v>
+      </c>
+      <c r="I553" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J553" s="3" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="554" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A554" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B554" s="3">
+        <v>1</v>
+      </c>
+      <c r="C554" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D554" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E554" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F554" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G554" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H554" s="3">
+        <v>643</v>
+      </c>
+      <c r="I554" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J554" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="555" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A555" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B555" s="3">
+        <v>7</v>
+      </c>
+      <c r="C555" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D555" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E555" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F555" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G555" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H555" s="3">
+        <v>185</v>
+      </c>
+      <c r="I555" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J555" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="556" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A556" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B556" s="3">
+        <v>7</v>
+      </c>
+      <c r="C556" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D556" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E556" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F556" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G556" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="H556" s="3">
+        <v>136</v>
+      </c>
+      <c r="I556" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J556" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="557" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A557" s="3" t="s">
+        <v>998</v>
+      </c>
+      <c r="B557" s="3">
+        <v>5</v>
+      </c>
+      <c r="C557" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D557" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E557" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F557" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G557" s="3" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H557" s="3">
+        <v>126</v>
+      </c>
+      <c r="I557" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J557" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="558" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A558" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B558" s="3">
+        <v>1</v>
+      </c>
+      <c r="C558" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D558" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E558" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F558" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G558" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="H558" s="3">
+        <v>69</v>
+      </c>
+      <c r="I558" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J558" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="559" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A559" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B559" s="3">
+        <v>1</v>
+      </c>
+      <c r="C559" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D559" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E559" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F559" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G559" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H559" s="3">
+        <v>126</v>
+      </c>
+      <c r="I559" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J559" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="560" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A560" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B560" s="3">
+        <v>8</v>
+      </c>
+      <c r="C560" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D560" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E560" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F560" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G560" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H560" s="3">
+        <v>609</v>
+      </c>
+      <c r="I560" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J560" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="561" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A561" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B561" s="3">
+        <v>2</v>
+      </c>
+      <c r="C561" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D561" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E561" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F561" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G561" s="3">
+        <v>2186397</v>
+      </c>
+      <c r="H561" s="3">
+        <v>119</v>
+      </c>
+      <c r="I561" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J561" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="562" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A562" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B562" s="3">
+        <v>4</v>
+      </c>
+      <c r="C562" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D562" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E562" s="3" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F562" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G562" s="3" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H562" s="3">
+        <v>131</v>
+      </c>
+      <c r="I562" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J562" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="563" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A563" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B563" s="3">
+        <v>4</v>
+      </c>
+      <c r="C563" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D563" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E563" s="3" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F563" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G563" s="3" t="s">
+        <v>1106</v>
+      </c>
+      <c r="H563" s="3">
+        <v>72</v>
+      </c>
+      <c r="I563" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J563" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="564" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A564" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B564" s="3">
+        <v>10</v>
+      </c>
+      <c r="C564" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D564" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E564" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F564" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G564" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H564" s="3">
+        <v>126</v>
+      </c>
+      <c r="I564" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J564" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="565" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A565" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B565" s="3">
+        <v>11</v>
+      </c>
+      <c r="C565" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D565" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="E565" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F565" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G565" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H565" s="3">
+        <v>311</v>
+      </c>
+      <c r="I565" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J565" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="566" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A566" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B566" s="3">
+        <v>9</v>
+      </c>
+      <c r="C566" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D566" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E566" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F566" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G566" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H566" s="3">
+        <v>126</v>
+      </c>
+      <c r="I566" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J566" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="567" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A567" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B567" s="3">
+        <v>5</v>
+      </c>
+      <c r="C567" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D567" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E567" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F567" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G567" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="H567" s="3">
+        <v>126</v>
+      </c>
+      <c r="I567" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J567" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="568" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A568" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B568" s="3">
+        <v>1</v>
+      </c>
+      <c r="C568" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D568" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E568" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F568" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G568" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="H568" s="3">
+        <v>72</v>
+      </c>
+      <c r="I568" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J568" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="569" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A569" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B569" s="3">
+        <v>3</v>
+      </c>
+      <c r="C569" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D569" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E569" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F569" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G569" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H569" s="3">
+        <v>233</v>
+      </c>
+      <c r="I569" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J569" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="570" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A570" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B570" s="3">
+        <v>11</v>
+      </c>
+      <c r="C570" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D570" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E570" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F570" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G570" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="H570" s="3">
+        <v>183</v>
+      </c>
+      <c r="I570" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J570" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="571" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A571" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B571" s="3">
+        <v>2</v>
+      </c>
+      <c r="C571" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D571" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E571" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F571" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G571" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="H571" s="3">
+        <v>398</v>
+      </c>
+      <c r="I571" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J571" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="572" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A572" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B572" s="3">
+        <v>1</v>
+      </c>
+      <c r="C572" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D572" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E572" s="3" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F572" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G572" s="3" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H572" s="3">
+        <v>193</v>
+      </c>
+      <c r="I572" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J572" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="573" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A573" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B573" s="3">
+        <v>1</v>
+      </c>
+      <c r="C573" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D573" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E573" s="3" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F573" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G573" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H573" s="3">
+        <v>205</v>
+      </c>
+      <c r="I573" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J573" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="574" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A574" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B574" s="3">
+        <v>1</v>
+      </c>
+      <c r="C574" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D574" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E574" s="3" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F574" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G574" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="H574" s="3">
+        <v>202</v>
+      </c>
+      <c r="I574" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J574" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="575" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A575" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B575" s="3">
+        <v>8</v>
+      </c>
+      <c r="C575" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D575" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="E575" s="3" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F575" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G575" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="H575" s="3">
+        <v>303</v>
+      </c>
+      <c r="I575" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J575" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="576" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A576" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B576" s="3">
+        <v>3</v>
+      </c>
+      <c r="C576" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D576" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E576" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F576" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G576" s="3">
+        <v>2185998</v>
+      </c>
+      <c r="H576" s="3">
+        <v>169</v>
+      </c>
+      <c r="I576" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J576" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="577" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A577" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B577" s="3">
+        <v>2</v>
+      </c>
+      <c r="C577" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D577" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E577" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F577" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G577" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H577" s="3">
+        <v>173</v>
+      </c>
+      <c r="I577" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J577" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="578" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A578" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B578" s="3">
+        <v>2</v>
+      </c>
+      <c r="C578" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D578" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E578" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F578" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G578" s="3">
+        <v>2185917</v>
+      </c>
+      <c r="H578" s="3">
+        <v>225</v>
+      </c>
+      <c r="I578" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J578" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="579" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A579" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B579" s="3">
+        <v>4</v>
+      </c>
+      <c r="C579" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D579" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E579" s="3" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F579" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G579" s="3" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H579" s="3">
+        <v>183</v>
+      </c>
+      <c r="I579" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J579" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="580" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A580" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B580" s="3">
+        <v>3</v>
+      </c>
+      <c r="C580" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D580" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E580" s="3" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F580" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G580" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="H580" s="3">
+        <v>183</v>
+      </c>
+      <c r="I580" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J580" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="581" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A581" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B581" s="3">
+        <v>1</v>
+      </c>
+      <c r="C581" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D581" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E581" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F581" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G581" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H581" s="3">
+        <v>169</v>
+      </c>
+      <c r="I581" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J581" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="582" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A582" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B582" s="3">
+        <v>1</v>
+      </c>
+      <c r="C582" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D582" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E582" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F582" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G582" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H582" s="3">
+        <v>138</v>
+      </c>
+      <c r="I582" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J582" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="583" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A583" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B583" s="3">
+        <v>16</v>
+      </c>
+      <c r="C583" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D583" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E583" s="3" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F583" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G583" s="3" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H583" s="3">
+        <v>72</v>
+      </c>
+      <c r="I583" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J583" s="3" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="584" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A584" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B584" s="3">
+        <v>4</v>
+      </c>
+      <c r="C584" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D584" s="3" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E584" s="3" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F584" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G584" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H584" s="3">
+        <v>199</v>
+      </c>
+      <c r="I584" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J584" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="585" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A585" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B585" s="3">
+        <v>1</v>
+      </c>
+      <c r="C585" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D585" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E585" s="3" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F585" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G585" s="3">
+        <v>2185745</v>
+      </c>
+      <c r="H585" s="3">
+        <v>129</v>
+      </c>
+      <c r="I585" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J585" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="586" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A586" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B586" s="3">
+        <v>3</v>
+      </c>
+      <c r="C586" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D586" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E586" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F586" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G586" s="3">
+        <v>2185736</v>
+      </c>
+      <c r="H586" s="3">
+        <v>125</v>
+      </c>
+      <c r="I586" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J586" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="587" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A587" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B587" s="3">
+        <v>4</v>
+      </c>
+      <c r="C587" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D587" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E587" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="F587" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G587" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H587" s="3">
+        <v>173</v>
+      </c>
+      <c r="I587" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J587" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="588" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A588" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B588" s="3">
+        <v>3</v>
+      </c>
+      <c r="C588" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D588" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E588" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F588" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G588" s="3">
+        <v>2185683</v>
+      </c>
+      <c r="H588" s="3">
+        <v>278</v>
+      </c>
+      <c r="I588" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J588" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="589" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A589" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B589" s="3">
+        <v>2</v>
+      </c>
+      <c r="C589" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D589" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E589" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F589" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G589" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H589" s="3">
+        <v>183</v>
+      </c>
+      <c r="I589" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J589" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="590" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A590" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B590" s="3">
+        <v>1</v>
+      </c>
+      <c r="C590" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D590" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E590" s="3" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F590" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G590" s="3">
+        <v>2185653</v>
+      </c>
+      <c r="H590" s="3">
+        <v>72</v>
+      </c>
+      <c r="I590" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J590" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="591" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A591" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B591" s="3">
+        <v>11</v>
+      </c>
+      <c r="C591" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D591" s="3" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E591" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F591" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G591" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H591" s="3">
+        <v>126</v>
+      </c>
+      <c r="I591" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J591" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="592" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A592" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B592" s="3">
+        <v>6</v>
+      </c>
+      <c r="C592" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D592" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E592" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F592" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G592" s="3" t="s">
+        <v>1162</v>
+      </c>
+      <c r="H592" s="3">
+        <v>252</v>
+      </c>
+      <c r="I592" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J592" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="593" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A593" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B593" s="3">
+        <v>6</v>
+      </c>
+      <c r="C593" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D593" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E593" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F593" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G593" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H593" s="3">
+        <v>255</v>
+      </c>
+      <c r="I593" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J593" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="594" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A594" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B594" s="3">
+        <v>6</v>
+      </c>
+      <c r="C594" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D594" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E594" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F594" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G594" s="3" t="s">
+        <v>1166</v>
+      </c>
+      <c r="H594" s="3">
+        <v>372</v>
+      </c>
+      <c r="I594" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J594" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="595" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A595" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B595" s="3">
+        <v>5</v>
+      </c>
+      <c r="C595" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D595" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E595" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F595" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G595" s="3" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H595" s="3">
+        <v>189</v>
+      </c>
+      <c r="I595" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J595" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="596" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A596" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B596" s="3">
+        <v>2</v>
+      </c>
+      <c r="C596" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D596" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="E596" s="3" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F596" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G596" s="3">
+        <v>2185448</v>
+      </c>
+      <c r="H596" s="3">
+        <v>125</v>
+      </c>
+      <c r="I596" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J596" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="597" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A597" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B597" s="3">
+        <v>1</v>
+      </c>
+      <c r="C597" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D597" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E597" s="3" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F597" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G597" s="3" t="s">
+        <v>1172</v>
+      </c>
+      <c r="H597" s="3">
+        <v>183</v>
+      </c>
+      <c r="I597" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J597" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="598" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A598" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B598" s="3">
+        <v>4</v>
+      </c>
+      <c r="C598" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D598" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E598" s="3" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F598" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G598" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H598" s="3">
+        <v>229</v>
+      </c>
+      <c r="I598" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J598" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="599" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A599" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B599" s="3">
+        <v>6</v>
+      </c>
+      <c r="C599" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D599" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E599" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F599" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G599" s="3" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H599" s="3">
+        <v>233</v>
+      </c>
+      <c r="I599" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J599" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="600" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A600" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B600" s="3">
+        <v>3</v>
+      </c>
+      <c r="C600" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D600" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E600" s="3" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F600" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G600" s="3" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H600" s="3">
+        <v>183</v>
+      </c>
+      <c r="I600" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J600" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="601" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A601" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B601" s="3">
+        <v>1</v>
+      </c>
+      <c r="C601" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D601" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="E601" s="3" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F601" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G601" s="3">
+        <v>2185293</v>
+      </c>
+      <c r="H601" s="3">
+        <v>72</v>
+      </c>
+      <c r="I601" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J601" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="602" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A602" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B602" s="3">
+        <v>3</v>
+      </c>
+      <c r="C602" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D602" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E602" s="3" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F602" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G602" s="3" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H602" s="3">
+        <v>183</v>
+      </c>
+      <c r="I602" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J602" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="603" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A603" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B603" s="3">
+        <v>7</v>
+      </c>
+      <c r="C603" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D603" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E603" s="3" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F603" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G603" s="3" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H603" s="3">
+        <v>69</v>
+      </c>
+      <c r="I603" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J603" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="604" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A604" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B604" s="3">
+        <v>1</v>
+      </c>
+      <c r="C604" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D604" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E604" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F604" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G604" s="3" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H604" s="3">
+        <v>69</v>
+      </c>
+      <c r="I604" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J604" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="605" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A605" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B605" s="3">
+        <v>3</v>
+      </c>
+      <c r="C605" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D605" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E605" s="3" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F605" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G605" s="3" t="s">
+        <v>1187</v>
+      </c>
+      <c r="H605" s="3">
+        <v>333</v>
+      </c>
+      <c r="I605" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J605" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="606" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A606" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B606" s="3">
+        <v>4</v>
+      </c>
+      <c r="C606" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D606" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E606" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F606" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G606" s="3" t="s">
+        <v>1189</v>
+      </c>
+      <c r="H606" s="3">
+        <v>126</v>
+      </c>
+      <c r="I606" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J606" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="607" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A607" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B607" s="3">
+        <v>1</v>
+      </c>
+      <c r="C607" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D607" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E607" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F607" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G607" s="3" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H607" s="3">
+        <v>193</v>
+      </c>
+      <c r="I607" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J607" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="608" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A608" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B608" s="3">
+        <v>2</v>
+      </c>
+      <c r="C608" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D608" s="3" t="s">
+        <v>1192</v>
+      </c>
+      <c r="E608" s="3" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F608" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G608" s="3">
+        <v>2185132</v>
+      </c>
+      <c r="H608" s="3">
+        <v>369</v>
+      </c>
+      <c r="I608" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J608" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="609" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A609" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B609" s="3">
+        <v>13</v>
+      </c>
+      <c r="C609" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D609" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E609" s="3" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F609" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G609" s="3" t="s">
+        <v>1195</v>
+      </c>
+      <c r="H609" s="3">
+        <v>173</v>
+      </c>
+      <c r="I609" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J609" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="610" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A610" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B610" s="3">
+        <v>6</v>
+      </c>
+      <c r="C610" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D610" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E610" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F610" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G610" s="3" t="s">
+        <v>1198</v>
+      </c>
+      <c r="H610" s="3">
+        <v>72</v>
+      </c>
+      <c r="I610" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J610" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="611" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A611" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B611" s="3">
+        <v>7</v>
+      </c>
+      <c r="C611" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D611" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E611" s="3" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F611" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G611" s="3" t="s">
+        <v>1200</v>
+      </c>
+      <c r="H611" s="3">
+        <v>181</v>
+      </c>
+      <c r="I611" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J611" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="612" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A612" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B612" s="3">
+        <v>1</v>
+      </c>
+      <c r="C612" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D612" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E612" s="3" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F612" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G612" s="3" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H612" s="3">
+        <v>69</v>
+      </c>
+      <c r="I612" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J612" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="613" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A613" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B613" s="3">
+        <v>9</v>
+      </c>
+      <c r="C613" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D613" s="3" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E613" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F613" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G613" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="H613" s="3">
+        <v>131</v>
+      </c>
+      <c r="I613" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J613" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="614" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A614" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B614" s="3">
+        <v>2</v>
+      </c>
+      <c r="C614" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D614" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E614" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F614" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G614" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="H614" s="3">
+        <v>67</v>
+      </c>
+      <c r="I614" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J614" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="615" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A615" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B615" s="3">
+        <v>2</v>
+      </c>
+      <c r="C615" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D615" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E615" s="3" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F615" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G615" s="3" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H615" s="3">
+        <v>189</v>
+      </c>
+      <c r="I615" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J615" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="616" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A616" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B616" s="3">
+        <v>2</v>
+      </c>
+      <c r="C616" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D616" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E616" s="3" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F616" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G616" s="3" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H616" s="3">
+        <v>183</v>
+      </c>
+      <c r="I616" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J616" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="617" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A617" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B617" s="3">
+        <v>1</v>
+      </c>
+      <c r="C617" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D617" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E617" s="3" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F617" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G617" s="3" t="s">
+        <v>1213</v>
+      </c>
+      <c r="H617" s="3">
+        <v>72</v>
+      </c>
+      <c r="I617" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J617" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="618" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A618" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B618" s="3">
+        <v>3</v>
+      </c>
+      <c r="C618" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D618" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E618" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="F618" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G618" s="3" t="s">
+        <v>1214</v>
+      </c>
+      <c r="H618" s="3">
+        <v>283</v>
+      </c>
+      <c r="I618" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J618" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="619" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A619" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B619" s="3">
+        <v>20</v>
+      </c>
+      <c r="C619" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D619" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E619" s="3" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F619" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G619" s="3" t="s">
+        <v>1216</v>
+      </c>
+      <c r="H619" s="3">
+        <v>126</v>
+      </c>
+      <c r="I619" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J619" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="620" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A620" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B620" s="3">
+        <v>1</v>
+      </c>
+      <c r="C620" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D620" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E620" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F620" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G620" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H620" s="3">
+        <v>136</v>
+      </c>
+      <c r="I620" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J620" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="621" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A621" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B621" s="3">
+        <v>8</v>
+      </c>
+      <c r="C621" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D621" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E621" s="3" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F621" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G621" s="3" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H621" s="3">
+        <v>183</v>
+      </c>
+      <c r="I621" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J621" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="622" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A622" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B622" s="3">
+        <v>7</v>
+      </c>
+      <c r="C622" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D622" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E622" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F622" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G622" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="H622" s="3">
+        <v>125</v>
+      </c>
+      <c r="I622" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J622" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="623" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A623" s="3" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B623" s="3">
+        <v>1</v>
+      </c>
+      <c r="C623" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D623" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E623" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F623" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G623" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="H623" s="3">
+        <v>198</v>
+      </c>
+      <c r="I623" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J623" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="624" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A624" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B624" s="3">
+        <v>1</v>
+      </c>
+      <c r="C624" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D624" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E624" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F624" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G624" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="H624" s="3">
+        <v>248</v>
+      </c>
+      <c r="I624" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J624" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="625" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A625" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B625" s="3">
+        <v>4</v>
+      </c>
+      <c r="C625" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D625" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E625" s="3" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F625" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G625" s="3" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H625" s="3">
+        <v>69</v>
+      </c>
+      <c r="I625" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J625" s="3" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="626" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A626" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B626" s="3">
+        <v>8</v>
+      </c>
+      <c r="C626" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D626" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="E626" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F626" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G626" s="3">
+        <v>2184404</v>
+      </c>
+      <c r="H626" s="3">
+        <v>75</v>
+      </c>
+      <c r="I626" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J626" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="627" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A627" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B627" s="3">
+        <v>4</v>
+      </c>
+      <c r="C627" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D627" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E627" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F627" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G627" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="H627" s="3">
+        <v>183</v>
+      </c>
+      <c r="I627" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J627" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="628" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A628" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B628" s="3">
+        <v>1</v>
+      </c>
+      <c r="C628" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D628" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E628" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F628" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G628" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="H628" s="3">
+        <v>193</v>
+      </c>
+      <c r="I628" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J628" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="629" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A629" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B629" s="3">
+        <v>2</v>
+      </c>
+      <c r="C629" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D629" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E629" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F629" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G629" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="H629" s="3">
+        <v>238</v>
+      </c>
+      <c r="I629" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J629" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="630" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A630" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B630" s="3">
+        <v>6</v>
+      </c>
+      <c r="C630" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D630" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E630" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F630" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G630" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="H630" s="3">
+        <v>62</v>
+      </c>
+      <c r="I630" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J630" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="631" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A631" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B631" s="3">
+        <v>2</v>
+      </c>
+      <c r="C631" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D631" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E631" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F631" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G631" s="3" t="s">
+        <v>1243</v>
+      </c>
+      <c r="H631" s="3">
+        <v>166</v>
+      </c>
+      <c r="I631" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J631" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="632" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A632" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B632" s="3">
+        <v>4</v>
+      </c>
+      <c r="C632" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D632" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E632" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F632" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G632" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="H632" s="3">
+        <v>325</v>
+      </c>
+      <c r="I632" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J632" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="633" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A633" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B633" s="3">
+        <v>3</v>
+      </c>
+      <c r="C633" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D633" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E633" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="F633" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G633" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="H633" s="3">
+        <v>183</v>
+      </c>
+      <c r="I633" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J633" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="634" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A634" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B634" s="3">
+        <v>1</v>
+      </c>
+      <c r="C634" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D634" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E634" s="3" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F634" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G634" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="H634" s="3">
+        <v>173</v>
+      </c>
+      <c r="I634" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J634" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="635" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A635" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B635" s="3">
+        <v>4</v>
+      </c>
+      <c r="C635" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D635" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E635" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G635" s="3">
+        <v>2184050</v>
+      </c>
+      <c r="H635" s="3">
+        <v>139</v>
+      </c>
+      <c r="I635" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J635" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="636" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A636" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B636" s="3">
+        <v>4</v>
+      </c>
+      <c r="C636" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D636" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E636" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F636" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G636" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H636" s="3">
+        <v>507</v>
+      </c>
+      <c r="I636" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J636" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="637" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A637" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B637" s="3">
+        <v>3</v>
+      </c>
+      <c r="C637" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D637" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E637" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F637" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G637" s="3" t="s">
+        <v>1254</v>
+      </c>
+      <c r="H637" s="3">
+        <v>129.15</v>
+      </c>
+      <c r="I637" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J637" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="638" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A638" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B638" s="3">
+        <v>1</v>
+      </c>
+      <c r="C638" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D638" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E638" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F638" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G638" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="H638" s="3">
+        <v>69</v>
+      </c>
+      <c r="I638" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J638" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="639" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A639" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B639" s="3">
+        <v>2</v>
+      </c>
+      <c r="C639" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D639" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E639" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F639" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G639" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="H639" s="3">
+        <v>72</v>
+      </c>
+      <c r="I639" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J639" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="640" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A640" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B640" s="3">
+        <v>3</v>
+      </c>
+      <c r="C640" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D640" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E640" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="F640" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G640" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="H640" s="3">
+        <v>67</v>
+      </c>
+      <c r="I640" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J640" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="641" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A641" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B641" s="3">
+        <v>1</v>
+      </c>
+      <c r="C641" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D641" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E641" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F641" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G641" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="H641" s="3">
+        <v>69</v>
+      </c>
+      <c r="I641" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J641" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="642" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A642" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B642" s="3">
+        <v>6</v>
+      </c>
+      <c r="C642" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D642" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E642" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F642" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G642" s="3" t="s">
+        <v>1263</v>
+      </c>
+      <c r="H642" s="3">
+        <v>126</v>
+      </c>
+      <c r="I642" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J642" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="643" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A643" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B643" s="3">
+        <v>1</v>
+      </c>
+      <c r="C643" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D643" s="3" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E643" s="3" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F643" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G643" s="3" t="s">
+        <v>1266</v>
+      </c>
+      <c r="H643" s="3">
+        <v>72</v>
+      </c>
+      <c r="I643" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J643" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="644" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A644" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B644" s="3">
+        <v>1</v>
+      </c>
+      <c r="C644" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D644" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E644" s="3" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F644" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G644" s="3">
+        <v>2183666</v>
+      </c>
+      <c r="H644" s="3">
+        <v>119</v>
+      </c>
+      <c r="I644" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J644" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="645" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A645" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B645" s="3">
+        <v>4</v>
+      </c>
+      <c r="C645" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D645" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E645" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F645" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G645" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="H645" s="3">
+        <v>183</v>
+      </c>
+      <c r="I645" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J645" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="646" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A646" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B646" s="3">
+        <v>2</v>
+      </c>
+      <c r="C646" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D646" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E646" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F646" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G646" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="H646" s="3">
+        <v>303</v>
+      </c>
+      <c r="I646" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J646" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="647" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A647" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B647" s="3">
+        <v>3</v>
+      </c>
+      <c r="C647" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D647" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E647" s="3" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F647" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G647" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="H647" s="3">
+        <v>183</v>
+      </c>
+      <c r="I647" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J647" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="648" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A648" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B648" s="3">
+        <v>24</v>
+      </c>
+      <c r="C648" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D648" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E648" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F648" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G648" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="H648" s="3">
+        <v>537</v>
+      </c>
+      <c r="I648" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J648" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="649" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A649" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B649" s="3">
+        <v>3</v>
+      </c>
+      <c r="C649" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D649" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E649" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F649" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G649" s="3" t="s">
+        <v>1277</v>
+      </c>
+      <c r="H649" s="3">
+        <v>269</v>
+      </c>
+      <c r="I649" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J649" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="650" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A650" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B650" s="3">
+        <v>5</v>
+      </c>
+      <c r="C650" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D650" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E650" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F650" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G650" s="3" t="s">
+        <v>1279</v>
+      </c>
+      <c r="H650" s="3">
+        <v>156</v>
+      </c>
+      <c r="I650" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J650" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="651" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A651" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B651" s="3">
+        <v>5</v>
+      </c>
+      <c r="C651" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D651" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E651" s="3" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F651" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G651" s="3" t="s">
+        <v>1280</v>
+      </c>
+      <c r="H651" s="3">
+        <v>373</v>
+      </c>
+      <c r="I651" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J651" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="652" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A652" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B652" s="3">
+        <v>2</v>
+      </c>
+      <c r="C652" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D652" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="E652" s="3" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F652" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G652" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H652" s="3">
+        <v>69</v>
+      </c>
+      <c r="I652" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J652" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="653" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A653" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B653" s="3">
+        <v>1</v>
+      </c>
+      <c r="C653" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D653" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E653" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F653" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G653" s="3" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H653" s="3">
+        <v>441</v>
+      </c>
+      <c r="I653" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J653" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="654" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A654" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B654" s="3">
+        <v>1</v>
+      </c>
+      <c r="C654" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D654" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E654" s="3" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F654" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G654" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="H654" s="3">
+        <v>195</v>
+      </c>
+      <c r="I654" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J654" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="655" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A655" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B655" s="3">
+        <v>20</v>
+      </c>
+      <c r="C655" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D655" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E655" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="F655" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G655" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="H655" s="3">
+        <v>199</v>
+      </c>
+      <c r="I655" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J655" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="656" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A656" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B656" s="3">
+        <v>3</v>
+      </c>
+      <c r="C656" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D656" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E656" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F656" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G656" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="H656" s="3">
+        <v>126</v>
+      </c>
+      <c r="I656" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J656" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="657" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A657" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B657" s="3">
+        <v>11</v>
+      </c>
+      <c r="C657" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D657" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E657" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F657" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G657" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="H657" s="3">
+        <v>133</v>
+      </c>
+      <c r="I657" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J657" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="658" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A658" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B658" s="3">
+        <v>1</v>
+      </c>
+      <c r="C658" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D658" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E658" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F658" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G658" s="3">
+        <v>2183387</v>
+      </c>
+      <c r="H658" s="3">
+        <v>119</v>
+      </c>
+      <c r="I658" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="J658" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="659" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A659" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B659" s="3">
+        <v>36</v>
+      </c>
+      <c r="C659" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D659" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E659" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F659" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G659" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H659" s="3">
+        <v>126</v>
+      </c>
+      <c r="I659" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J659" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="660" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A660" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B660" s="3">
+        <v>1</v>
+      </c>
+      <c r="C660" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D660" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E660" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G660" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H660" s="3">
+        <v>193</v>
+      </c>
+      <c r="I660" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J660" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="661" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A661" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B661" s="3">
+        <v>1</v>
+      </c>
+      <c r="C661" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D661" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E661" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G661" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H661" s="3">
+        <v>69</v>
+      </c>
+      <c r="I661" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J661" s="3" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="662" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A662" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B662" s="3">
+        <v>1</v>
+      </c>
+      <c r="C662" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D662" s="3" t="s">
+        <v>1228</v>
+      </c>
+      <c r="E662" s="3" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G662" s="3" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H662" s="3">
+        <v>69</v>
+      </c>
+      <c r="I662" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J662" s="3" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="663" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A663" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B663" s="3">
+        <v>1</v>
+      </c>
+      <c r="C663" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D663" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E663" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G663" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H663" s="3">
+        <v>339.05</v>
+      </c>
+      <c r="I663" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J663" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="664" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A664" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B664" s="3">
+        <v>4</v>
+      </c>
+      <c r="C664" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D664" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E664" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G664" s="3">
+        <v>2183148</v>
+      </c>
+      <c r="H664" s="3">
+        <v>53</v>
+      </c>
+      <c r="I664" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J664" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="665" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A665" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B665" s="3">
+        <v>6</v>
+      </c>
+      <c r="C665" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D665" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E665" s="3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G665" s="3" t="s">
+        <v>1309</v>
+      </c>
+      <c r="H665" s="3">
+        <v>173</v>
+      </c>
+      <c r="I665" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J665" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="666" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A666" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B666" s="3">
+        <v>2</v>
+      </c>
+      <c r="C666" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D666" s="3" t="s">
+        <v>1042</v>
+      </c>
+      <c r="E666" s="3" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G666" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="H666" s="3">
+        <v>116.1</v>
+      </c>
+      <c r="I666" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J666" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="667" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A667" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B667" s="3">
+        <v>2</v>
+      </c>
+      <c r="C667" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D667" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E667" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G667" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H667" s="3">
+        <v>183</v>
+      </c>
+      <c r="I667" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J667" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="668" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A668" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B668" s="3">
+        <v>3</v>
+      </c>
+      <c r="C668" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D668" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E668" s="3" t="s">
+        <v>1314</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G668" s="3" t="s">
+        <v>1315</v>
+      </c>
+      <c r="H668" s="3">
+        <v>726</v>
+      </c>
+      <c r="I668" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J668" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="669" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A669" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B669" s="3">
+        <v>5</v>
+      </c>
+      <c r="C669" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D669" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E669" s="3" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G669" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H669" s="3">
+        <v>66</v>
+      </c>
+      <c r="I669" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J669" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="670" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A670" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B670" s="3">
+        <v>5</v>
+      </c>
+      <c r="C670" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D670" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E670" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G670" s="3">
+        <v>2182775</v>
+      </c>
+      <c r="H670" s="3">
+        <v>129</v>
+      </c>
+      <c r="I670" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J670" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="671" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A671" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B671" s="3">
+        <v>3</v>
+      </c>
+      <c r="C671" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D671" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E671" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G671" s="3" t="s">
+        <v>1320</v>
+      </c>
+      <c r="H671" s="3">
+        <v>248</v>
+      </c>
+      <c r="I671" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J671" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="672" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A672" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B672" s="3">
+        <v>1</v>
+      </c>
+      <c r="C672" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D672" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E672" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G672" s="3" t="s">
+        <v>1322</v>
+      </c>
+      <c r="H672" s="3">
+        <v>133.95</v>
+      </c>
+      <c r="I672" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J672" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="673" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A673" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B673" s="3">
+        <v>1</v>
+      </c>
+      <c r="C673" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D673" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="E673" s="3" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G673" s="3" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H673" s="3">
+        <v>193</v>
+      </c>
+      <c r="I673" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J673" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="674" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A674" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B674" s="3">
+        <v>2</v>
+      </c>
+      <c r="C674" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D674" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E674" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G674" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H674" s="3">
+        <v>329</v>
+      </c>
+      <c r="I674" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J674" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="675" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A675" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B675" s="3">
+        <v>4</v>
+      </c>
+      <c r="C675" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D675" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E675" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G675" s="3" t="s">
+        <v>1328</v>
+      </c>
+      <c r="H675" s="3">
+        <v>185</v>
+      </c>
+      <c r="I675" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J675" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="676" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A676" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B676" s="3">
+        <v>1</v>
+      </c>
+      <c r="C676" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D676" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E676" s="3" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G676" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="H676" s="3">
+        <v>126</v>
+      </c>
+      <c r="I676" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J676" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="677" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A677" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B677" s="3">
+        <v>1</v>
+      </c>
+      <c r="C677" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D677" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E677" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G677" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="H677" s="3">
+        <v>183</v>
+      </c>
+      <c r="I677" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J677" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="678" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A678" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B678" s="3">
+        <v>1</v>
+      </c>
+      <c r="C678" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D678" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="E678" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G678" s="3" t="s">
+        <v>1335</v>
+      </c>
+      <c r="H678" s="3">
+        <v>192</v>
+      </c>
+      <c r="I678" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J678" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="679" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A679" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B679" s="3">
+        <v>6</v>
+      </c>
+      <c r="C679" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D679" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E679" s="3" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G679" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="H679" s="3">
+        <v>126</v>
+      </c>
+      <c r="I679" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J679" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="680" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A680" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B680" s="3">
+        <v>4</v>
+      </c>
+      <c r="C680" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D680" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E680" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G680" s="3">
+        <v>2182309</v>
+      </c>
+      <c r="H680" s="3">
+        <v>129</v>
+      </c>
+      <c r="I680" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J680" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="681" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A681" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B681" s="3">
+        <v>1</v>
+      </c>
+      <c r="C681" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D681" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E681" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G681" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="H681" s="3">
+        <v>72</v>
+      </c>
+      <c r="I681" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J681" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="682" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A682" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B682" s="3">
+        <v>4</v>
+      </c>
+      <c r="C682" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D682" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E682" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="F682" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G682" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H682" s="3">
+        <v>131</v>
+      </c>
+      <c r="I682" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J682" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="683" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A683" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B683" s="3">
+        <v>1</v>
+      </c>
+      <c r="C683" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D683" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E683" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F683" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G683" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="H683" s="3">
+        <v>193</v>
+      </c>
+      <c r="I683" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J683" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="684" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A684" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B684" s="3">
+        <v>2</v>
+      </c>
+      <c r="C684" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D684" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E684" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F684" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G684" s="3" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H684" s="3">
+        <v>141</v>
+      </c>
+      <c r="I684" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J684" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="685" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A685" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B685" s="3">
+        <v>6</v>
+      </c>
+      <c r="C685" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D685" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="E685" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G685" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="H685" s="3">
+        <v>126</v>
+      </c>
+      <c r="I685" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J685" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/orders.xlsx
+++ b/orders.xlsx
@@ -7844,7 +7844,7 @@
         <v>10</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>11</v>
@@ -12214,7 +12214,7 @@
         <v>356</v>
       </c>
       <c r="H151" s="3">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>12</v>
@@ -14180,7 +14180,7 @@
         <v>432</v>
       </c>
       <c r="B213" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C213" s="3" t="s">
         <v>11</v>
@@ -18180,7 +18180,7 @@
         <v>683</v>
       </c>
       <c r="B338" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>11</v>
@@ -18774,7 +18774,7 @@
         <v>2206336</v>
       </c>
       <c r="H356" s="3">
-        <v>219</v>
+        <v>50</v>
       </c>
       <c r="I356" s="3" t="s">
         <v>104</v>
@@ -21412,7 +21412,7 @@
         <v>893</v>
       </c>
       <c r="B439" s="3">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C439" s="3" t="s">
         <v>11</v>
@@ -22532,7 +22532,7 @@
         <v>955</v>
       </c>
       <c r="B474" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C474" s="3" t="s">
         <v>18</v>
@@ -26212,7 +26212,7 @@
         <v>1177</v>
       </c>
       <c r="B589" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C589" s="3" t="s">
         <v>11</v>
@@ -27972,7 +27972,7 @@
         <v>1242</v>
       </c>
       <c r="B644" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C644" s="3" t="s">
         <v>11</v>
@@ -29092,7 +29092,7 @@
         <v>1337</v>
       </c>
       <c r="B679" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C679" s="3" t="s">
         <v>11</v>
@@ -31620,7 +31620,7 @@
         <v>1474</v>
       </c>
       <c r="B758" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C758" s="3" t="s">
         <v>11</v>
@@ -34084,7 +34084,7 @@
         <v>1609</v>
       </c>
       <c r="B835" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C835" s="3" t="s">
         <v>18</v>
@@ -40484,7 +40484,7 @@
         <v>1927</v>
       </c>
       <c r="B1035" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C1035" s="3" t="s">
         <v>11</v>
@@ -43844,7 +43844,7 @@
         <v>2150</v>
       </c>
       <c r="B1140" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C1140" s="3" t="s">
         <v>11</v>
@@ -45028,7 +45028,7 @@
         <v>2205</v>
       </c>
       <c r="B1177" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C1177" s="3" t="s">
         <v>11</v>
